--- a/tools/luban/MiniTemplate/Datas/demo.manyKey.xlsx
+++ b/tools/luban/MiniTemplate/Datas/demo.manyKey.xlsx
@@ -131,7 +131,7 @@
     <t>Circle,2,10.5</t>
   </si>
   <si>
-    <t>abc</t>
+    <t>k1</t>
   </si>
   <si>
     <t>道具2</t>
